--- a/update-mapping-section/ig/StructureDefinition-fr-lm-transfusion-de-produits-sanguins.xlsx
+++ b/update-mapping-section/ig/StructureDefinition-fr-lm-transfusion-de-produits-sanguins.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T15:27:44+00:00</t>
+    <t>2026-08-12T09:25:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
